--- a/Beta_CAPM/beta_capm_calculator.xlsx
+++ b/Beta_CAPM/beta_capm_calculator.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://northeastern-my.sharepoint.com/personal/s_mandal_northeastern_edu/Documents/Youtube_Video/Finance/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sohommandal/Downloads/github/youtubedemo/Beta_CAPM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="111" documentId="11_EEB4144C56B65352B6AD7888028CE83BBD3BAF7D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F556380-1124-6445-A948-BE1660394560}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F402BEA-3120-D04B-8085-EDF03935978D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23740" yWindow="460" windowWidth="28860" windowHeight="17980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio CAPM" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="67">
   <si>
     <t>Portfolio Beta and CAPM Calculator</t>
   </si>
@@ -223,18 +223,6 @@
   </si>
   <si>
     <t>TC Energy</t>
-  </si>
-  <si>
-    <t>Portfolio Weight</t>
-  </si>
-  <si>
-    <t>Beta</t>
-  </si>
-  <si>
-    <t>Enbridge Inc.</t>
-  </si>
-  <si>
-    <t>TC Energy Corporation</t>
   </si>
   <si>
     <t>Microsoft</t>
@@ -952,7 +940,7 @@
         <v>0.13823529411764707</v>
       </c>
       <c r="H11" s="19">
-        <f>IF(E11="Yes",$C$4+D11*$C$6,"")</f>
+        <f t="shared" ref="H11:H22" si="0">IF(E11="Yes",$C$4+D11*$C$6,"")</f>
         <v>8.6399999999999991E-2</v>
       </c>
       <c r="I11" s="9"/>
@@ -974,15 +962,15 @@
         <v>45</v>
       </c>
       <c r="F12" s="20">
-        <f t="shared" ref="F11:F22" si="0">IF(E12="Yes",C12/SUMIF($E$11:$E$22,"Yes",$C$11:$C$22),0)</f>
+        <f t="shared" ref="F12:F22" si="1">IF(E12="Yes",C12/SUMIF($E$11:$E$22,"Yes",$C$11:$C$22),0)</f>
         <v>0.14705882352941177</v>
       </c>
       <c r="G12" s="20">
-        <f t="shared" ref="G12:G22" si="1">IF(E12="Yes",F12*D12,0)</f>
+        <f t="shared" ref="G12:G22" si="2">IF(E12="Yes",F12*D12,0)</f>
         <v>0.12941176470588237</v>
       </c>
       <c r="H12" s="20">
-        <f>IF(E12="Yes",$C$4+D12*$C$6,"")</f>
+        <f t="shared" si="0"/>
         <v>8.2799999999999999E-2</v>
       </c>
       <c r="I12" s="12"/>
@@ -1004,15 +992,15 @@
         <v>45</v>
       </c>
       <c r="F13" s="20">
+        <f t="shared" si="1"/>
+        <v>1.4705882352941176E-2</v>
+      </c>
+      <c r="G13" s="20">
+        <f t="shared" si="2"/>
+        <v>1.7102941176470588E-2</v>
+      </c>
+      <c r="H13" s="20">
         <f t="shared" si="0"/>
-        <v>1.4705882352941176E-2</v>
-      </c>
-      <c r="G13" s="20">
-        <f t="shared" si="1"/>
-        <v>1.7102941176470588E-2</v>
-      </c>
-      <c r="H13" s="20">
-        <f>IF(E13="Yes",$C$4+D13*$C$6,"")</f>
         <v>9.9779999999999994E-2</v>
       </c>
       <c r="I13" s="12"/>
@@ -1034,15 +1022,15 @@
         <v>45</v>
       </c>
       <c r="F14" s="20">
+        <f t="shared" si="1"/>
+        <v>1.4705882352941176E-2</v>
+      </c>
+      <c r="G14" s="20">
+        <f t="shared" si="2"/>
+        <v>2.7058823529411767E-2</v>
+      </c>
+      <c r="H14" s="20">
         <f t="shared" si="0"/>
-        <v>1.4705882352941176E-2</v>
-      </c>
-      <c r="G14" s="20">
-        <f t="shared" si="1"/>
-        <v>2.7058823529411767E-2</v>
-      </c>
-      <c r="H14" s="20">
-        <f>IF(E14="Yes",$C$4+D14*$C$6,"")</f>
         <v>0.1404</v>
       </c>
       <c r="I14" s="12"/>
@@ -1064,15 +1052,15 @@
         <v>45</v>
       </c>
       <c r="F15" s="20">
+        <f t="shared" si="1"/>
+        <v>1.4705882352941176E-2</v>
+      </c>
+      <c r="G15" s="20">
+        <f t="shared" si="2"/>
+        <v>1.8794117647058822E-2</v>
+      </c>
+      <c r="H15" s="20">
         <f t="shared" si="0"/>
-        <v>1.4705882352941176E-2</v>
-      </c>
-      <c r="G15" s="20">
-        <f t="shared" si="1"/>
-        <v>1.8794117647058822E-2</v>
-      </c>
-      <c r="H15" s="20">
-        <f>IF(E15="Yes",$C$4+D15*$C$6,"")</f>
         <v>0.10668</v>
       </c>
       <c r="I15" s="12"/>
@@ -1094,15 +1082,15 @@
         <v>45</v>
       </c>
       <c r="F16" s="20">
+        <f t="shared" si="1"/>
+        <v>1.4705882352941176E-2</v>
+      </c>
+      <c r="G16" s="20">
+        <f t="shared" si="2"/>
+        <v>1.7794117647058821E-2</v>
+      </c>
+      <c r="H16" s="20">
         <f t="shared" si="0"/>
-        <v>1.4705882352941176E-2</v>
-      </c>
-      <c r="G16" s="20">
-        <f t="shared" si="1"/>
-        <v>1.7794117647058821E-2</v>
-      </c>
-      <c r="H16" s="20">
-        <f>IF(E16="Yes",$C$4+D16*$C$6,"")</f>
         <v>0.1026</v>
       </c>
       <c r="I16" s="12"/>
@@ -1124,15 +1112,15 @@
         <v>45</v>
       </c>
       <c r="F17" s="20">
+        <f t="shared" si="1"/>
+        <v>1.4705882352941176E-2</v>
+      </c>
+      <c r="G17" s="20">
+        <f t="shared" si="2"/>
+        <v>1.186764705882353E-2</v>
+      </c>
+      <c r="H17" s="20">
         <f t="shared" si="0"/>
-        <v>1.4705882352941176E-2</v>
-      </c>
-      <c r="G17" s="20">
-        <f t="shared" si="1"/>
-        <v>1.186764705882353E-2</v>
-      </c>
-      <c r="H17" s="20">
-        <f>IF(E17="Yes",$C$4+D17*$C$6,"")</f>
         <v>7.8420000000000004E-2</v>
       </c>
       <c r="I17" s="12"/>
@@ -1154,15 +1142,15 @@
         <v>45</v>
       </c>
       <c r="F18" s="20">
+        <f t="shared" si="1"/>
+        <v>1.4705882352941176E-2</v>
+      </c>
+      <c r="G18" s="20">
+        <f t="shared" si="2"/>
+        <v>1.1470588235294118E-2</v>
+      </c>
+      <c r="H18" s="20">
         <f t="shared" si="0"/>
-        <v>1.4705882352941176E-2</v>
-      </c>
-      <c r="G18" s="20">
-        <f t="shared" si="1"/>
-        <v>1.1470588235294118E-2</v>
-      </c>
-      <c r="H18" s="20">
-        <f>IF(E18="Yes",$C$4+D18*$C$6,"")</f>
         <v>7.6800000000000007E-2</v>
       </c>
       <c r="I18" s="12"/>
@@ -1184,15 +1172,15 @@
         <v>45</v>
       </c>
       <c r="F19" s="20">
+        <f t="shared" si="1"/>
+        <v>1.4705882352941176E-2</v>
+      </c>
+      <c r="G19" s="20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H19" s="20">
         <f t="shared" si="0"/>
-        <v>1.4705882352941176E-2</v>
-      </c>
-      <c r="G19" s="20">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H19" s="20">
-        <f>IF(E19="Yes",$C$4+D19*$C$6,"")</f>
         <v>0.03</v>
       </c>
       <c r="I19" s="12"/>
@@ -1214,25 +1202,25 @@
         <v>45</v>
       </c>
       <c r="F20" s="20">
+        <f t="shared" si="1"/>
+        <v>1.4705882352941176E-2</v>
+      </c>
+      <c r="G20" s="20">
+        <f t="shared" si="2"/>
+        <v>1.4367647058823528E-2</v>
+      </c>
+      <c r="H20" s="20">
         <f t="shared" si="0"/>
-        <v>1.4705882352941176E-2</v>
-      </c>
-      <c r="G20" s="20">
-        <f t="shared" si="1"/>
-        <v>1.4367647058823528E-2</v>
-      </c>
-      <c r="H20" s="20">
-        <f>IF(E20="Yes",$C$4+D20*$C$6,"")</f>
         <v>8.8620000000000004E-2</v>
       </c>
       <c r="I20" s="12"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C21" s="16">
         <v>2000</v>
@@ -1244,25 +1232,25 @@
         <v>45</v>
       </c>
       <c r="F21" s="20">
+        <f t="shared" si="1"/>
+        <v>0.29411764705882354</v>
+      </c>
+      <c r="G21" s="20">
+        <f t="shared" si="2"/>
+        <v>0.3235294117647059</v>
+      </c>
+      <c r="H21" s="20">
         <f t="shared" si="0"/>
-        <v>0.29411764705882354</v>
-      </c>
-      <c r="G21" s="20">
-        <f t="shared" si="1"/>
-        <v>0.3235294117647059</v>
-      </c>
-      <c r="H21" s="20">
-        <f>IF(E21="Yes",$C$4+D21*$C$6,"")</f>
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="I21" s="12"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C22" s="16">
         <v>2000</v>
@@ -1274,15 +1262,15 @@
         <v>45</v>
       </c>
       <c r="F22" s="21">
+        <f t="shared" si="1"/>
+        <v>0.29411764705882354</v>
+      </c>
+      <c r="G22" s="21">
+        <f t="shared" si="2"/>
+        <v>0.36470588235294121</v>
+      </c>
+      <c r="H22" s="21">
         <f t="shared" si="0"/>
-        <v>0.29411764705882354</v>
-      </c>
-      <c r="G22" s="21">
-        <f t="shared" si="1"/>
-        <v>0.36470588235294121</v>
-      </c>
-      <c r="H22" s="21">
-        <f>IF(E22="Yes",$C$4+D22*$C$6,"")</f>
         <v>0.10439999999999999</v>
       </c>
       <c r="I22" s="15"/>
@@ -1323,158 +1311,40 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="15">
-      <c r="F30" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>64</v>
-      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="F31" t="s">
-        <v>47</v>
-      </c>
-      <c r="G31" t="s">
-        <v>48</v>
-      </c>
-      <c r="H31" s="4">
-        <v>8.2000000000000003E-2</v>
-      </c>
-      <c r="I31">
-        <v>0.94</v>
-      </c>
+      <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:9">
-      <c r="F32" t="s">
-        <v>49</v>
-      </c>
-      <c r="G32" t="s">
-        <v>17</v>
-      </c>
-      <c r="H32" s="4">
-        <v>4.7E-2</v>
-      </c>
-      <c r="I32">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="33" spans="6:9">
-      <c r="F33" t="s">
-        <v>50</v>
-      </c>
-      <c r="G33" t="s">
-        <v>51</v>
-      </c>
-      <c r="H33" s="4">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="I33">
-        <v>1.163</v>
-      </c>
-    </row>
-    <row r="34" spans="6:9">
-      <c r="F34" t="s">
-        <v>52</v>
-      </c>
-      <c r="G34" t="s">
-        <v>53</v>
-      </c>
-      <c r="H34" s="4">
-        <v>3.2000000000000001E-2</v>
-      </c>
-      <c r="I34">
-        <v>1.84</v>
-      </c>
-    </row>
-    <row r="35" spans="6:9">
-      <c r="F35" t="s">
-        <v>54</v>
-      </c>
-      <c r="G35" t="s">
-        <v>15</v>
-      </c>
-      <c r="H35" s="4">
-        <v>3.1E-2</v>
-      </c>
-      <c r="I35">
-        <v>1.278</v>
-      </c>
-    </row>
-    <row r="36" spans="6:9">
-      <c r="F36" t="s">
-        <v>55</v>
-      </c>
-      <c r="G36" t="s">
-        <v>56</v>
-      </c>
-      <c r="H36" s="4">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="I36">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="37" spans="6:9">
-      <c r="F37" t="s">
-        <v>65</v>
-      </c>
-      <c r="G37" t="s">
-        <v>16</v>
-      </c>
-      <c r="H37" s="4">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="I37">
-        <v>0.80700000000000005</v>
-      </c>
-    </row>
-    <row r="38" spans="6:9">
-      <c r="F38" t="s">
-        <v>58</v>
-      </c>
-      <c r="G38" t="s">
-        <v>59</v>
-      </c>
-      <c r="H38" s="4">
-        <v>2.4E-2</v>
-      </c>
-      <c r="I38">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="39" spans="6:9">
-      <c r="F39" t="s">
-        <v>60</v>
-      </c>
-      <c r="G39" t="s">
-        <v>61</v>
-      </c>
-      <c r="H39" s="4">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="6:9">
-      <c r="F40" t="s">
-        <v>66</v>
-      </c>
-      <c r="G40" t="s">
-        <v>18</v>
-      </c>
-      <c r="H40" s="4">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="I40">
-        <v>0.97699999999999998</v>
-      </c>
+      <c r="H32" s="4"/>
+    </row>
+    <row r="33" spans="8:8">
+      <c r="H33" s="4"/>
+    </row>
+    <row r="34" spans="8:8">
+      <c r="H34" s="4"/>
+    </row>
+    <row r="35" spans="8:8">
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36" spans="8:8">
+      <c r="H36" s="4"/>
+    </row>
+    <row r="37" spans="8:8">
+      <c r="H37" s="4"/>
+    </row>
+    <row r="38" spans="8:8">
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" spans="8:8">
+      <c r="H39" s="4"/>
+    </row>
+    <row r="40" spans="8:8">
+      <c r="H40" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
